--- a/닉네임인증이벤트엑셀.xlsx
+++ b/닉네임인증이벤트엑셀.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\파이썬\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CC3A0C-0D73-4519-972A-4E42A7815B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFACC834-E23E-41D8-8C86-0D2AD77EECD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="840" windowWidth="28800" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="225">
   <si>
     <t>페이지</t>
   </si>
@@ -47,691 +47,667 @@
     <t>카페닉네임</t>
   </si>
   <si>
-    <t>11075</t>
-  </si>
-  <si>
-    <t>시인아이</t>
-  </si>
-  <si>
-    <t>방빈이</t>
-  </si>
-  <si>
-    <t>11073</t>
-  </si>
-  <si>
-    <t>P용신</t>
-  </si>
-  <si>
-    <t>11070</t>
-  </si>
-  <si>
-    <t>양루</t>
-  </si>
-  <si>
-    <t>11069</t>
-  </si>
-  <si>
-    <t>가람찬</t>
-  </si>
-  <si>
-    <t>11067</t>
-  </si>
-  <si>
-    <t>원소</t>
-  </si>
-  <si>
-    <t>11063</t>
-  </si>
-  <si>
-    <t>노을</t>
-  </si>
-  <si>
-    <t>11059</t>
-  </si>
-  <si>
-    <t>라큐</t>
-  </si>
-  <si>
-    <t>11058</t>
-  </si>
-  <si>
-    <t>Leddie</t>
-  </si>
-  <si>
-    <t>11057</t>
-  </si>
-  <si>
-    <t>인천이대산</t>
-  </si>
-  <si>
-    <t>11045</t>
-  </si>
-  <si>
-    <t>배기진스</t>
-  </si>
-  <si>
-    <t>11041</t>
-  </si>
-  <si>
-    <t>해즈</t>
-  </si>
-  <si>
-    <t>11038</t>
-  </si>
-  <si>
-    <t>zzzyu</t>
-  </si>
-  <si>
-    <t>11031</t>
-  </si>
-  <si>
-    <t>규미니</t>
-  </si>
-  <si>
-    <t>11028</t>
-  </si>
-  <si>
-    <t>국민주</t>
-  </si>
-  <si>
-    <t>11025</t>
-  </si>
-  <si>
-    <t>sh</t>
-  </si>
-  <si>
-    <t>sh1</t>
-  </si>
-  <si>
-    <t>11022</t>
-  </si>
-  <si>
-    <t>독도지킴이</t>
-  </si>
-  <si>
-    <t>11019</t>
-  </si>
-  <si>
-    <t>레오양운</t>
-  </si>
-  <si>
-    <t>아이스아메리카누</t>
-  </si>
-  <si>
-    <t>11013</t>
-  </si>
-  <si>
-    <t>보석바</t>
-  </si>
-  <si>
-    <t>11010</t>
-  </si>
-  <si>
-    <t>아침먹고가</t>
-  </si>
-  <si>
-    <t>오환무</t>
-  </si>
-  <si>
-    <t>11007</t>
-  </si>
-  <si>
-    <t>포식</t>
-  </si>
-  <si>
-    <t>11002</t>
-  </si>
-  <si>
-    <t>조선아이</t>
-  </si>
-  <si>
-    <t>10998</t>
-  </si>
-  <si>
-    <t>찌타</t>
-  </si>
-  <si>
-    <t>10994</t>
-  </si>
-  <si>
-    <t>랑스</t>
-  </si>
-  <si>
-    <t>10992</t>
-  </si>
-  <si>
-    <t>원거리탱커</t>
-  </si>
-  <si>
-    <t>10988</t>
-  </si>
-  <si>
-    <t>pangit</t>
-  </si>
-  <si>
-    <t>10984</t>
-  </si>
-  <si>
-    <t>고윤정</t>
-  </si>
-  <si>
-    <t>10970</t>
-  </si>
-  <si>
-    <t>릭레리</t>
-  </si>
-  <si>
-    <t>10967</t>
-  </si>
-  <si>
-    <t>roy</t>
-  </si>
-  <si>
-    <t>gurumi</t>
-  </si>
-  <si>
-    <t>10958</t>
-  </si>
-  <si>
-    <t>왕하칠무해</t>
-  </si>
-  <si>
-    <t>10951</t>
-  </si>
-  <si>
-    <t>휘인</t>
-  </si>
-  <si>
-    <t>10944</t>
-  </si>
-  <si>
-    <t>끼야아옹</t>
-  </si>
-  <si>
-    <t>10934</t>
-  </si>
-  <si>
-    <t>hulee</t>
-  </si>
-  <si>
-    <t>10925</t>
-  </si>
-  <si>
-    <t>샤오위</t>
-  </si>
-  <si>
-    <t>10924</t>
-  </si>
-  <si>
-    <t>쿠쮜</t>
-  </si>
-  <si>
-    <t>10918</t>
-  </si>
-  <si>
-    <t>플라타너스s</t>
-  </si>
-  <si>
-    <t>10910</t>
-  </si>
-  <si>
-    <t>황재균</t>
-  </si>
-  <si>
-    <t>10905</t>
-  </si>
-  <si>
-    <t>신문왕</t>
-  </si>
-  <si>
-    <t>10903</t>
-  </si>
-  <si>
-    <t>귤꽁</t>
-  </si>
-  <si>
-    <t>10895</t>
-  </si>
-  <si>
-    <t>아오키지</t>
-  </si>
-  <si>
-    <t>10893</t>
-  </si>
-  <si>
-    <t>식스팩</t>
-  </si>
-  <si>
-    <t>10892</t>
-  </si>
-  <si>
-    <t>백기</t>
-  </si>
-  <si>
-    <t>눈점</t>
-  </si>
-  <si>
-    <t>10887</t>
-  </si>
-  <si>
-    <t>미삐순</t>
-  </si>
-  <si>
-    <t>10886</t>
-  </si>
-  <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>10882</t>
-  </si>
-  <si>
-    <t>nimboos</t>
-  </si>
-  <si>
-    <t>10875</t>
-  </si>
-  <si>
-    <t>가원</t>
-  </si>
-  <si>
-    <t>10873</t>
-  </si>
-  <si>
-    <t>갸지니</t>
-  </si>
-  <si>
-    <t>10867</t>
-  </si>
-  <si>
-    <t>화초</t>
-  </si>
-  <si>
-    <t>10858</t>
-  </si>
-  <si>
-    <t>애매리카노</t>
-  </si>
-  <si>
-    <t>10855</t>
-  </si>
-  <si>
-    <t>레전필</t>
-  </si>
-  <si>
-    <t>10853</t>
-  </si>
-  <si>
-    <t>무노좋아</t>
-  </si>
-  <si>
-    <t>두산</t>
-  </si>
-  <si>
-    <t>10847</t>
-  </si>
-  <si>
-    <t>이더존버</t>
-  </si>
-  <si>
-    <t>10845</t>
-  </si>
-  <si>
-    <t>흑호령</t>
-  </si>
-  <si>
-    <t>aon</t>
-  </si>
-  <si>
-    <t>10839</t>
-  </si>
-  <si>
-    <t>독고독0</t>
-  </si>
-  <si>
-    <t>10829</t>
-  </si>
-  <si>
-    <t>샤라</t>
-  </si>
-  <si>
-    <t>10827</t>
-  </si>
-  <si>
-    <t>이겜재밋나</t>
-  </si>
-  <si>
-    <t>10824</t>
-  </si>
-  <si>
-    <t>변화</t>
-  </si>
-  <si>
-    <t>10821</t>
-  </si>
-  <si>
-    <t>메밀대장군</t>
-  </si>
-  <si>
-    <t>10820</t>
-  </si>
-  <si>
-    <t>그장띵띵띵이</t>
-  </si>
-  <si>
-    <t>그랩장인띵훈이</t>
-  </si>
-  <si>
-    <t>10816</t>
-  </si>
-  <si>
-    <t>김경수</t>
-  </si>
-  <si>
-    <t>인면목</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>프나즐</t>
-  </si>
-  <si>
-    <t>센스</t>
-  </si>
-  <si>
-    <t>10806</t>
-  </si>
-  <si>
-    <t>젤이쁜울아덜</t>
-  </si>
-  <si>
-    <t>10800</t>
-  </si>
-  <si>
-    <t>또롱센세</t>
-  </si>
-  <si>
-    <t>10797</t>
-  </si>
-  <si>
-    <t>임춘봉</t>
-  </si>
-  <si>
-    <t>10794</t>
-  </si>
-  <si>
-    <t>마노</t>
-  </si>
-  <si>
-    <t>10790</t>
-  </si>
-  <si>
-    <t>깐즈</t>
-  </si>
-  <si>
-    <t>깐즈맘</t>
-  </si>
-  <si>
-    <t>10784</t>
-  </si>
-  <si>
-    <t>솜이빠</t>
-  </si>
-  <si>
-    <t>10781</t>
-  </si>
-  <si>
-    <t>rubidu</t>
-  </si>
-  <si>
-    <t>10779</t>
-  </si>
-  <si>
-    <t>불사대마왕</t>
-  </si>
-  <si>
-    <t>10778</t>
-  </si>
-  <si>
-    <t>요괴</t>
-  </si>
-  <si>
-    <t>민또</t>
-  </si>
-  <si>
-    <t>10772</t>
-  </si>
-  <si>
-    <t>고짬덮</t>
-  </si>
-  <si>
-    <t>10771</t>
-  </si>
-  <si>
-    <t>왁구</t>
-  </si>
-  <si>
-    <t>10769</t>
-  </si>
-  <si>
-    <t>유강체</t>
-  </si>
-  <si>
-    <t>강채</t>
-  </si>
-  <si>
-    <t>10763</t>
-  </si>
-  <si>
-    <t>률밤</t>
-  </si>
-  <si>
-    <t>10748</t>
-  </si>
-  <si>
-    <t>블러디하트</t>
-  </si>
-  <si>
-    <t>덩기</t>
-  </si>
-  <si>
-    <t>10742</t>
-  </si>
-  <si>
-    <t>새콤달콤짱</t>
-  </si>
-  <si>
-    <t>크라운새콤</t>
-  </si>
-  <si>
-    <t>10719</t>
-  </si>
-  <si>
-    <t>퓨즈티</t>
-  </si>
-  <si>
-    <t>10715</t>
-  </si>
-  <si>
-    <t>ABLYN</t>
-  </si>
-  <si>
-    <t>Ablyn</t>
-  </si>
-  <si>
-    <t>10709</t>
-  </si>
-  <si>
-    <t>이상설</t>
-  </si>
-  <si>
-    <t>10705</t>
-  </si>
-  <si>
-    <t>장수척준경</t>
-  </si>
-  <si>
-    <t>10702</t>
-  </si>
-  <si>
-    <t>본드류</t>
-  </si>
-  <si>
-    <t>깨수깡</t>
-  </si>
-  <si>
-    <t>10701</t>
-  </si>
-  <si>
-    <t>아한</t>
-  </si>
-  <si>
-    <t>10699</t>
-  </si>
-  <si>
-    <t>한능검사</t>
-  </si>
-  <si>
-    <t>배세영</t>
-  </si>
-  <si>
-    <t>10694</t>
-  </si>
-  <si>
-    <t>모름님님</t>
-  </si>
-  <si>
-    <t>10689</t>
-  </si>
-  <si>
-    <t>도르섬</t>
-  </si>
-  <si>
-    <t>10682</t>
-  </si>
-  <si>
-    <t>이릿</t>
-  </si>
-  <si>
-    <t>10678</t>
-  </si>
-  <si>
-    <t>피렛</t>
-  </si>
-  <si>
-    <t>10676</t>
-  </si>
-  <si>
-    <t>한글로6자</t>
-  </si>
-  <si>
-    <t>10674</t>
-  </si>
-  <si>
-    <t>꺄르47</t>
-  </si>
-  <si>
-    <t>10666</t>
-  </si>
-  <si>
-    <t>윤이파파</t>
-  </si>
-  <si>
-    <t>10658</t>
-  </si>
-  <si>
-    <t>한국사장인</t>
-  </si>
-  <si>
-    <t>10656</t>
-  </si>
-  <si>
-    <t>고졸무직백수</t>
-  </si>
-  <si>
-    <t>10653</t>
-  </si>
-  <si>
-    <t>투농</t>
-  </si>
-  <si>
-    <t>10646</t>
-  </si>
-  <si>
-    <t>우렁</t>
-  </si>
-  <si>
-    <t>10642</t>
-  </si>
-  <si>
-    <t>천지</t>
-  </si>
-  <si>
-    <t>10625</t>
-  </si>
-  <si>
-    <t>퐈이야뱃</t>
-  </si>
-  <si>
-    <t>10623</t>
-  </si>
-  <si>
-    <t>신비블루</t>
-  </si>
-  <si>
-    <t>10621</t>
-  </si>
-  <si>
-    <t>김창식씌</t>
-  </si>
-  <si>
-    <t>10617</t>
-  </si>
-  <si>
-    <t>바스토</t>
-  </si>
-  <si>
-    <t>10615</t>
-  </si>
-  <si>
-    <t>깜트절미</t>
-  </si>
-  <si>
-    <t>10608</t>
+    <t>12428</t>
+  </si>
+  <si>
+    <t>동해바다거북</t>
+  </si>
+  <si>
+    <t>12423</t>
+  </si>
+  <si>
+    <t>허스칼</t>
+  </si>
+  <si>
+    <t>12421</t>
+  </si>
+  <si>
+    <t>봄베이</t>
+  </si>
+  <si>
+    <t>12416</t>
+  </si>
+  <si>
+    <t>셔니</t>
+  </si>
+  <si>
+    <t>12414</t>
+  </si>
+  <si>
+    <t>롯데리아</t>
+  </si>
+  <si>
+    <t>12412</t>
+  </si>
+  <si>
+    <t>때수건빡빡낼름</t>
+  </si>
+  <si>
+    <t>12408</t>
+  </si>
+  <si>
+    <t>주뇨리</t>
+  </si>
+  <si>
+    <t>12404</t>
+  </si>
+  <si>
+    <t>엘린s</t>
+  </si>
+  <si>
+    <t>12401</t>
+  </si>
+  <si>
+    <t>유성</t>
+  </si>
+  <si>
+    <t>12395</t>
+  </si>
+  <si>
+    <t>미루하루</t>
+  </si>
+  <si>
+    <t>미르하루</t>
+  </si>
+  <si>
+    <t>12394</t>
+  </si>
+  <si>
+    <t>반짝였던</t>
+  </si>
+  <si>
+    <t>탈모왕두피</t>
+  </si>
+  <si>
+    <t>12390</t>
+  </si>
+  <si>
+    <t>웅그리</t>
+  </si>
+  <si>
+    <t>12387</t>
+  </si>
+  <si>
+    <t>빽곰샘</t>
+  </si>
+  <si>
+    <t>12383</t>
+  </si>
+  <si>
+    <t>Mutalisk</t>
+  </si>
+  <si>
+    <t>12380</t>
+  </si>
+  <si>
+    <t>자리해라</t>
+  </si>
+  <si>
+    <t>힘좀내야지</t>
+  </si>
+  <si>
+    <t>12377</t>
+  </si>
+  <si>
+    <t>쑤우니</t>
+  </si>
+  <si>
+    <t>12371</t>
+  </si>
+  <si>
+    <t>뮤랭</t>
+  </si>
+  <si>
+    <t>12370</t>
+  </si>
+  <si>
+    <t>댕심</t>
+  </si>
+  <si>
+    <t>12369</t>
+  </si>
+  <si>
+    <t>난치</t>
+  </si>
+  <si>
+    <t>12362</t>
+  </si>
+  <si>
+    <t>웅취</t>
+  </si>
+  <si>
+    <t>12361</t>
+  </si>
+  <si>
+    <t>수아비</t>
+  </si>
+  <si>
+    <t>12357</t>
+  </si>
+  <si>
+    <t>ryu1gyu</t>
+  </si>
+  <si>
+    <t>12355</t>
+  </si>
+  <si>
+    <t>유진버프</t>
+  </si>
+  <si>
+    <t>12354</t>
+  </si>
+  <si>
+    <t>BUG</t>
+  </si>
+  <si>
+    <t>Bug</t>
+  </si>
+  <si>
+    <t>12342</t>
+  </si>
+  <si>
+    <t>노코</t>
+  </si>
+  <si>
+    <t>12338</t>
+  </si>
+  <si>
+    <t>평범한인간</t>
+  </si>
+  <si>
+    <t>12334</t>
+  </si>
+  <si>
+    <t>빙그리</t>
+  </si>
+  <si>
+    <t>12331</t>
+  </si>
+  <si>
+    <t>두오링</t>
+  </si>
+  <si>
+    <t>12325</t>
+  </si>
+  <si>
+    <t>최이</t>
+  </si>
+  <si>
+    <t>최영</t>
+  </si>
+  <si>
+    <t>12322</t>
+  </si>
+  <si>
+    <t>류라온</t>
+  </si>
+  <si>
+    <t>라혼</t>
+  </si>
+  <si>
+    <t>12319</t>
+  </si>
+  <si>
+    <t>Roq</t>
+  </si>
+  <si>
+    <t>12313</t>
+  </si>
+  <si>
+    <t>잔혹이</t>
+  </si>
+  <si>
+    <t>12306</t>
+  </si>
+  <si>
+    <t>당감표류남</t>
+  </si>
+  <si>
+    <t>12300</t>
+  </si>
+  <si>
+    <t>뿡빵핑</t>
+  </si>
+  <si>
+    <t>12295</t>
+  </si>
+  <si>
+    <t>구조</t>
+  </si>
+  <si>
+    <t>12283</t>
+  </si>
+  <si>
+    <t>내금위장</t>
+  </si>
+  <si>
+    <t>12278</t>
+  </si>
+  <si>
+    <t>칼있나</t>
+  </si>
+  <si>
+    <t>12275</t>
+  </si>
+  <si>
+    <t>읭용</t>
+  </si>
+  <si>
+    <t>후루사</t>
+  </si>
+  <si>
+    <t>12270</t>
+  </si>
+  <si>
+    <t>한지민</t>
+  </si>
+  <si>
+    <t>12268</t>
+  </si>
+  <si>
+    <t>무한표류기</t>
+  </si>
+  <si>
+    <t>12260</t>
+  </si>
+  <si>
+    <t>만리독행</t>
+  </si>
+  <si>
+    <t>12256</t>
+  </si>
+  <si>
+    <t>twvking</t>
+  </si>
+  <si>
+    <t>12254</t>
+  </si>
+  <si>
+    <t>봉구덕구</t>
+  </si>
+  <si>
+    <t>12250</t>
+  </si>
+  <si>
+    <t>하슬란</t>
+  </si>
+  <si>
+    <t>12246</t>
+  </si>
+  <si>
+    <t>소금상자</t>
+  </si>
+  <si>
+    <t>12238</t>
+  </si>
+  <si>
+    <t>만자이</t>
+  </si>
+  <si>
+    <t>12235</t>
+  </si>
+  <si>
+    <t>우비님</t>
+  </si>
+  <si>
+    <t>12231</t>
+  </si>
+  <si>
+    <t>요로롱도로롱</t>
+  </si>
+  <si>
+    <t>12229</t>
+  </si>
+  <si>
+    <t>IFONLY</t>
+  </si>
+  <si>
+    <t>12223</t>
+  </si>
+  <si>
+    <t>김철헌</t>
+  </si>
+  <si>
+    <t>12220</t>
+  </si>
+  <si>
+    <t>김빠오</t>
+  </si>
+  <si>
+    <t>12212</t>
+  </si>
+  <si>
+    <t>언박</t>
+  </si>
+  <si>
+    <t>12210</t>
+  </si>
+  <si>
+    <t>12205</t>
+  </si>
+  <si>
+    <t>칼라일</t>
+  </si>
+  <si>
+    <t>12199</t>
+  </si>
+  <si>
+    <t>부레옥잠</t>
+  </si>
+  <si>
+    <t>12191</t>
+  </si>
+  <si>
+    <t>Isear</t>
+  </si>
+  <si>
+    <t>12189</t>
+  </si>
+  <si>
+    <t>그린중앙</t>
+  </si>
+  <si>
+    <t>멋있는인생</t>
+  </si>
+  <si>
+    <t>12184</t>
+  </si>
+  <si>
+    <t>헨젤과그랬대</t>
+  </si>
+  <si>
+    <t>12177</t>
+  </si>
+  <si>
+    <t>나일세세종</t>
+  </si>
+  <si>
+    <t>12171</t>
+  </si>
+  <si>
+    <t>바닥</t>
+  </si>
+  <si>
+    <t>시리우리스</t>
+  </si>
+  <si>
+    <t>12160</t>
+  </si>
+  <si>
+    <t>도로욜</t>
+  </si>
+  <si>
+    <t>12158</t>
+  </si>
+  <si>
+    <t>개떵이</t>
+  </si>
+  <si>
+    <t>12151</t>
+  </si>
+  <si>
+    <t>때오</t>
+  </si>
+  <si>
+    <t>12146</t>
+  </si>
+  <si>
+    <t>우리나라만세</t>
+  </si>
+  <si>
+    <t>12144</t>
+  </si>
+  <si>
+    <t>뺙뺙빡뺙빡뺙</t>
+  </si>
+  <si>
+    <t>12139</t>
+  </si>
+  <si>
+    <t>바닐라아포카토</t>
+  </si>
+  <si>
+    <t>12135</t>
+  </si>
+  <si>
+    <t>태양초</t>
+  </si>
+  <si>
+    <t>12129</t>
+  </si>
+  <si>
+    <t>차매</t>
+  </si>
+  <si>
+    <t>12122</t>
+  </si>
+  <si>
+    <t>홀릭스</t>
+  </si>
+  <si>
+    <t>12119</t>
+  </si>
+  <si>
+    <t>허슥히</t>
+  </si>
+  <si>
+    <t>12116</t>
+  </si>
+  <si>
+    <t>오란비</t>
+  </si>
+  <si>
+    <t>12105</t>
+  </si>
+  <si>
+    <t>린다만</t>
+  </si>
+  <si>
+    <t>12097</t>
+  </si>
+  <si>
+    <t>데네브</t>
+  </si>
+  <si>
+    <t>12092</t>
+  </si>
+  <si>
+    <t>박뱅장</t>
+  </si>
+  <si>
+    <t>12090</t>
+  </si>
+  <si>
+    <t>홍es</t>
+  </si>
+  <si>
+    <t>12087</t>
+  </si>
+  <si>
+    <t>빨간맛</t>
+  </si>
+  <si>
+    <t>단원평가</t>
+  </si>
+  <si>
+    <t>12084</t>
+  </si>
+  <si>
+    <t>진접대장</t>
+  </si>
+  <si>
+    <t>12078</t>
+  </si>
+  <si>
+    <t>쉬폭</t>
+  </si>
+  <si>
+    <t>12076</t>
+  </si>
+  <si>
+    <t>기짜니짱</t>
+  </si>
+  <si>
+    <t>12074</t>
+  </si>
+  <si>
+    <t>난세영웅임</t>
+  </si>
+  <si>
+    <t>12070</t>
+  </si>
+  <si>
+    <t>햇콩이</t>
+  </si>
+  <si>
+    <t>12066</t>
+  </si>
+  <si>
+    <t>라온65</t>
+  </si>
+  <si>
+    <t>라온파파12</t>
+  </si>
+  <si>
+    <t>12065</t>
+  </si>
+  <si>
+    <t>임나영</t>
+  </si>
+  <si>
+    <t>12062</t>
+  </si>
+  <si>
+    <t>극락주식회사</t>
+  </si>
+  <si>
+    <t>퐝씨</t>
+  </si>
+  <si>
+    <t>12056</t>
+  </si>
+  <si>
+    <t>무비니삼촌</t>
+  </si>
+  <si>
+    <t>12054</t>
+  </si>
+  <si>
+    <t>인터느</t>
+  </si>
+  <si>
+    <t>12052</t>
+  </si>
+  <si>
+    <t>raonao</t>
+  </si>
+  <si>
+    <t>12049</t>
+  </si>
+  <si>
+    <t>김가네</t>
+  </si>
+  <si>
+    <t>12045</t>
+  </si>
+  <si>
+    <t>남아당자강</t>
+  </si>
+  <si>
+    <t>12038</t>
+  </si>
+  <si>
+    <t>쑥쑥이</t>
+  </si>
+  <si>
+    <t>12036</t>
+  </si>
+  <si>
+    <t>민정</t>
+  </si>
+  <si>
+    <t>12035</t>
+  </si>
+  <si>
+    <t>최민기</t>
+  </si>
+  <si>
+    <t>12034</t>
+  </si>
+  <si>
+    <t>요괴소녀</t>
+  </si>
+  <si>
+    <t>12030</t>
+  </si>
+  <si>
+    <t>난세표루깅</t>
+  </si>
+  <si>
+    <t>12029</t>
+  </si>
+  <si>
+    <t>Early</t>
+  </si>
+  <si>
+    <t>12028</t>
+  </si>
+  <si>
+    <t>창하</t>
+  </si>
+  <si>
+    <t>12025</t>
   </si>
   <si>
     <t>GM김준</t>
   </si>
   <si>
-    <t>10604</t>
-  </si>
-  <si>
-    <t>H쥬드</t>
-  </si>
-  <si>
-    <t>10602</t>
-  </si>
-  <si>
-    <t>김찬종</t>
-  </si>
-  <si>
-    <t>10596</t>
-  </si>
-  <si>
-    <t>이훈</t>
-  </si>
-  <si>
-    <t>10594</t>
-  </si>
-  <si>
-    <t>쥬리찌유</t>
-  </si>
-  <si>
-    <t>10590</t>
-  </si>
-  <si>
-    <t>상구링</t>
+    <t>12024</t>
+  </si>
+  <si>
+    <t>박씨아저씨</t>
+  </si>
+  <si>
+    <t>12022</t>
+  </si>
+  <si>
+    <t>qeadws</t>
+  </si>
+  <si>
+    <t>12019</t>
+  </si>
+  <si>
+    <t>22KaKa</t>
+  </si>
+  <si>
+    <t>12013</t>
+  </si>
+  <si>
+    <t>화니짱짱</t>
+  </si>
+  <si>
+    <t>12009</t>
+  </si>
+  <si>
+    <t>판테라</t>
+  </si>
+  <si>
+    <t>12006</t>
+  </si>
+  <si>
+    <t>묵흔</t>
+  </si>
+  <si>
+    <t>12005</t>
+  </si>
+  <si>
+    <t>윤서봉</t>
+  </si>
+  <si>
+    <t>12001</t>
+  </si>
+  <si>
+    <t>슬기윤서</t>
   </si>
 </sst>
 </file>
@@ -1125,13 +1101,13 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1139,13 +1115,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C3" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D3" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1153,13 +1129,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1167,13 +1143,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1181,13 +1157,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D6" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1195,10 +1171,13 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>221</v>
+        <v>213</v>
+      </c>
+      <c r="C7" t="s">
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1206,13 +1185,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C8" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1220,13 +1199,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D9" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1234,13 +1213,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D10" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1248,13 +1224,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C11" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1262,13 +1238,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1276,13 +1252,13 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C13" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1290,13 +1266,10 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>207</v>
-      </c>
-      <c r="C14" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D14" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1304,13 +1277,13 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1318,13 +1291,10 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
-      </c>
-      <c r="C16" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D16" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1332,13 +1302,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D17" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1346,13 +1316,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C18" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1360,13 +1330,13 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C19" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1374,13 +1344,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D20" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1388,13 +1358,13 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D21" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1402,13 +1372,13 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C22" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D22" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1416,13 +1386,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C23" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D23" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1430,13 +1400,13 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C24" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D24" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1444,13 +1414,13 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1458,13 +1428,13 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C26" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D26" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1472,13 +1442,13 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C27" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D27" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1486,13 +1456,13 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C28" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D28" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1500,13 +1470,13 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C29" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D29" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1514,13 +1484,13 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D30" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1528,13 +1498,13 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C31" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D31" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1542,13 +1512,13 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1556,13 +1526,13 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C33" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D33" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1570,13 +1540,13 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1584,13 +1554,13 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C35" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1598,13 +1568,13 @@
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1612,13 +1582,13 @@
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D37" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1626,13 +1596,13 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D38" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1640,13 +1610,13 @@
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C39" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D39" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1654,13 +1624,13 @@
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1668,10 +1638,13 @@
         <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="C41" t="s">
+        <v>143</v>
       </c>
       <c r="D41" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1679,13 +1652,13 @@
         <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1693,13 +1666,13 @@
         <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1707,13 +1680,13 @@
         <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1721,13 +1694,13 @@
         <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1735,13 +1708,13 @@
         <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1749,13 +1722,13 @@
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1763,13 +1736,13 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1777,13 +1750,10 @@
         <v>4</v>
       </c>
       <c r="B49" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" t="s">
         <v>126</v>
-      </c>
-      <c r="C49" t="s">
-        <v>127</v>
-      </c>
-      <c r="D49" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1791,13 +1761,13 @@
         <v>4</v>
       </c>
       <c r="B50" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" t="s">
+        <v>123</v>
+      </c>
+      <c r="D50" t="s">
         <v>124</v>
-      </c>
-      <c r="C50" t="s">
-        <v>125</v>
-      </c>
-      <c r="D50" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1805,13 +1775,13 @@
         <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1819,13 +1789,13 @@
         <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C52" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1833,13 +1803,13 @@
         <v>4</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1847,13 +1817,13 @@
         <v>4</v>
       </c>
       <c r="B54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D54" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1867,7 +1837,7 @@
         <v>114</v>
       </c>
       <c r="D55" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1877,6 +1847,9 @@
       <c r="B56" t="s">
         <v>111</v>
       </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
       <c r="D56" t="s">
         <v>112</v>
       </c>
@@ -1886,10 +1859,10 @@
         <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D57" t="s">
         <v>110</v>
@@ -1900,13 +1873,13 @@
         <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -1914,13 +1887,13 @@
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C59" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D59" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1928,13 +1901,13 @@
         <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1942,13 +1915,13 @@
         <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C61" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D61" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -1956,13 +1929,13 @@
         <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C62" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D62" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -1970,13 +1943,10 @@
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
-      </c>
-      <c r="C63" t="s">
         <v>97</v>
       </c>
       <c r="D63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -1984,13 +1954,13 @@
         <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -1998,13 +1968,13 @@
         <v>3</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C65" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -2012,13 +1982,13 @@
         <v>3</v>
       </c>
       <c r="B66" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D66" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -2026,13 +1996,10 @@
         <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D67" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -2040,13 +2007,10 @@
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>85</v>
-      </c>
-      <c r="C68" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2054,13 +2018,13 @@
         <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D69" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -2068,10 +2032,13 @@
         <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="C70" t="s">
+        <v>83</v>
       </c>
       <c r="D70" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -2079,13 +2046,13 @@
         <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D71" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -2093,13 +2060,13 @@
         <v>3</v>
       </c>
       <c r="B72" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -2107,13 +2074,13 @@
         <v>3</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -2121,13 +2088,13 @@
         <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -2135,13 +2102,13 @@
         <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -2149,13 +2116,13 @@
         <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -2169,7 +2136,7 @@
         <v>68</v>
       </c>
       <c r="D77" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -2177,10 +2144,10 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
+        <v>64</v>
+      </c>
+      <c r="C78" t="s">
         <v>65</v>
-      </c>
-      <c r="C78" t="s">
-        <v>66</v>
       </c>
       <c r="D78" t="s">
         <v>66</v>
@@ -2197,7 +2164,7 @@
         <v>63</v>
       </c>
       <c r="D79" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -2235,6 +2202,9 @@
       <c r="B82" t="s">
         <v>56</v>
       </c>
+      <c r="C82" t="s">
+        <v>57</v>
+      </c>
       <c r="D82" t="s">
         <v>57</v>
       </c>
@@ -2244,10 +2214,10 @@
         <v>2</v>
       </c>
       <c r="B83" t="s">
+        <v>53</v>
+      </c>
+      <c r="C83" t="s">
         <v>54</v>
-      </c>
-      <c r="C83" t="s">
-        <v>55</v>
       </c>
       <c r="D83" t="s">
         <v>55</v>
@@ -2258,13 +2228,13 @@
         <v>2</v>
       </c>
       <c r="B84" t="s">
+        <v>51</v>
+      </c>
+      <c r="C84" t="s">
         <v>52</v>
       </c>
-      <c r="C84" t="s">
-        <v>53</v>
-      </c>
       <c r="D84" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -2272,13 +2242,10 @@
         <v>2</v>
       </c>
       <c r="B85" t="s">
+        <v>49</v>
+      </c>
+      <c r="D85" t="s">
         <v>50</v>
-      </c>
-      <c r="C85" t="s">
-        <v>51</v>
-      </c>
-      <c r="D85" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -2286,13 +2253,13 @@
         <v>2</v>
       </c>
       <c r="B86" t="s">
+        <v>47</v>
+      </c>
+      <c r="C86" t="s">
         <v>48</v>
       </c>
-      <c r="C86" t="s">
-        <v>49</v>
-      </c>
       <c r="D86" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -2300,13 +2267,13 @@
         <v>2</v>
       </c>
       <c r="B87" t="s">
+        <v>45</v>
+      </c>
+      <c r="C87" t="s">
         <v>46</v>
       </c>
-      <c r="C87" t="s">
-        <v>47</v>
-      </c>
       <c r="D87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -2320,7 +2287,7 @@
         <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -2330,9 +2297,6 @@
       <c r="B89" t="s">
         <v>41</v>
       </c>
-      <c r="C89" t="s">
-        <v>42</v>
-      </c>
       <c r="D89" t="s">
         <v>42</v>
       </c>
@@ -2342,10 +2306,10 @@
         <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C90" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D90" t="s">
         <v>40</v>
@@ -2356,13 +2320,13 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C91" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D91" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -2370,13 +2334,13 @@
         <v>1</v>
       </c>
       <c r="B92" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C92" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D92" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -2384,13 +2348,13 @@
         <v>1</v>
       </c>
       <c r="B93" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C93" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D93" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -2398,13 +2362,10 @@
         <v>1</v>
       </c>
       <c r="B94" t="s">
-        <v>29</v>
-      </c>
-      <c r="C94" t="s">
         <v>30</v>
       </c>
       <c r="D94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -2412,13 +2373,13 @@
         <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D95" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -2428,8 +2389,11 @@
       <c r="B96" t="s">
         <v>25</v>
       </c>
+      <c r="C96" t="s">
+        <v>26</v>
+      </c>
       <c r="D96" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -2437,10 +2401,10 @@
         <v>1</v>
       </c>
       <c r="B97" t="s">
+        <v>22</v>
+      </c>
+      <c r="C97" t="s">
         <v>23</v>
-      </c>
-      <c r="C97" t="s">
-        <v>24</v>
       </c>
       <c r="D97" t="s">
         <v>24</v>
@@ -2451,13 +2415,13 @@
         <v>1</v>
       </c>
       <c r="B98" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" t="s">
         <v>21</v>
       </c>
-      <c r="C98" t="s">
-        <v>22</v>
-      </c>
       <c r="D98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -2465,13 +2429,13 @@
         <v>1</v>
       </c>
       <c r="B99" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" t="s">
         <v>19</v>
       </c>
-      <c r="C99" t="s">
-        <v>20</v>
-      </c>
       <c r="D99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -2479,13 +2443,13 @@
         <v>1</v>
       </c>
       <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="s">
         <v>17</v>
       </c>
-      <c r="C100" t="s">
-        <v>18</v>
-      </c>
       <c r="D100" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -2493,13 +2457,13 @@
         <v>1</v>
       </c>
       <c r="B101" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101" t="s">
         <v>15</v>
       </c>
-      <c r="C101" t="s">
-        <v>16</v>
-      </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -2507,13 +2471,13 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" t="s">
         <v>13</v>
       </c>
-      <c r="C102" t="s">
-        <v>14</v>
-      </c>
       <c r="D102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -2521,13 +2485,13 @@
         <v>1</v>
       </c>
       <c r="B103" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" t="s">
         <v>11</v>
       </c>
-      <c r="C103" t="s">
-        <v>12</v>
-      </c>
       <c r="D103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -2535,13 +2499,13 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" t="s">
         <v>9</v>
       </c>
-      <c r="C104" t="s">
-        <v>10</v>
-      </c>
       <c r="D104" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -2549,13 +2513,10 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" t="s">
         <v>7</v>
-      </c>
-      <c r="C105" t="s">
-        <v>8</v>
-      </c>
-      <c r="D105" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -2569,7 +2530,7 @@
         <v>5</v>
       </c>
       <c r="D106" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
